--- a/referências.xlsx
+++ b/referências.xlsx
@@ -16,7 +16,7 @@
     <sheet name="destinos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">destinos!$A$1:$I$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">destinos!$A$1:$I$285</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">operador!$A$1:$G$156</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3152" uniqueCount="1569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3196" uniqueCount="1594">
   <si>
     <t>Iata Code</t>
   </si>
@@ -4747,6 +4747,81 @@
   </si>
   <si>
     <t>LC</t>
+  </si>
+  <si>
+    <t>MLM</t>
+  </si>
+  <si>
+    <t>Comlux Malta</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>Air Peace</t>
+  </si>
+  <si>
+    <t>APK</t>
+  </si>
+  <si>
+    <t>Air Peace Limited</t>
+  </si>
+  <si>
+    <t>QF</t>
+  </si>
+  <si>
+    <t>Qantas</t>
+  </si>
+  <si>
+    <t>QFA</t>
+  </si>
+  <si>
+    <t>Qantas Airways Limited</t>
+  </si>
+  <si>
+    <t>Sydney</t>
+  </si>
+  <si>
+    <t>YSSY</t>
+  </si>
+  <si>
+    <t>CUZ</t>
+  </si>
+  <si>
+    <t>Cuzco</t>
+  </si>
+  <si>
+    <t>SPZO</t>
+  </si>
+  <si>
+    <t>GI</t>
+  </si>
+  <si>
+    <t>Gridiron Air</t>
+  </si>
+  <si>
+    <t>RZN</t>
+  </si>
+  <si>
+    <t>Gridiron Air LLC</t>
+  </si>
+  <si>
+    <t>ARN</t>
+  </si>
+  <si>
+    <t>Aeronexus</t>
+  </si>
+  <si>
+    <t>Aeronexus Coorporate</t>
+  </si>
+  <si>
+    <t>STN</t>
+  </si>
+  <si>
+    <t>Stantsted</t>
+  </si>
+  <si>
+    <t>EGSS</t>
   </si>
 </sst>
 </file>
@@ -5102,20 +5177,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H156"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H160"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="67.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="15.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="67.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5138,7 +5213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -5161,7 +5236,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -5184,7 +5259,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -5207,7 +5282,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -5230,7 +5305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -5253,7 +5328,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
@@ -5276,7 +5351,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -5299,7 +5374,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
@@ -5322,7 +5397,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
@@ -5345,7 +5420,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>46</v>
       </c>
@@ -5368,7 +5443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>49</v>
       </c>
@@ -5391,7 +5466,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>53</v>
       </c>
@@ -5414,7 +5489,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>57</v>
       </c>
@@ -5437,7 +5512,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>60</v>
       </c>
@@ -5460,7 +5535,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>64</v>
       </c>
@@ -5483,7 +5558,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>68</v>
       </c>
@@ -5506,7 +5581,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>72</v>
       </c>
@@ -5529,7 +5604,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>76</v>
       </c>
@@ -5552,7 +5627,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>80</v>
       </c>
@@ -5575,7 +5650,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>84</v>
       </c>
@@ -5596,7 +5671,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>88</v>
       </c>
@@ -5619,7 +5694,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>92</v>
       </c>
@@ -5642,7 +5717,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>95</v>
       </c>
@@ -5665,7 +5740,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>98</v>
       </c>
@@ -5686,7 +5761,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>102</v>
       </c>
@@ -5709,7 +5784,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>104</v>
       </c>
@@ -5732,7 +5807,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>107</v>
       </c>
@@ -5755,7 +5830,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>110</v>
       </c>
@@ -5778,7 +5853,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>113</v>
       </c>
@@ -5801,7 +5876,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>117</v>
       </c>
@@ -5824,7 +5899,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>122</v>
       </c>
@@ -5847,7 +5922,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>126</v>
       </c>
@@ -5870,7 +5945,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>129</v>
       </c>
@@ -5893,7 +5968,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>133</v>
       </c>
@@ -5916,7 +5991,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>137</v>
       </c>
@@ -5939,7 +6014,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>139</v>
       </c>
@@ -5960,7 +6035,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>146</v>
       </c>
@@ -5983,7 +6058,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>150</v>
       </c>
@@ -6006,7 +6081,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>153</v>
       </c>
@@ -6029,7 +6104,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>157</v>
       </c>
@@ -6052,7 +6127,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>160</v>
       </c>
@@ -6075,7 +6150,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>163</v>
       </c>
@@ -6096,7 +6171,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>167</v>
       </c>
@@ -6119,7 +6194,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>815</v>
       </c>
@@ -6142,7 +6217,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>173</v>
       </c>
@@ -6165,7 +6240,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>175</v>
       </c>
@@ -6188,7 +6263,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>179</v>
       </c>
@@ -6211,7 +6286,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>183</v>
       </c>
@@ -6234,7 +6309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>186</v>
       </c>
@@ -6255,7 +6330,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>190</v>
       </c>
@@ -6276,7 +6351,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>193</v>
       </c>
@@ -6299,7 +6374,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>197</v>
       </c>
@@ -6320,7 +6395,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>201</v>
       </c>
@@ -6343,7 +6418,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>205</v>
       </c>
@@ -6366,7 +6441,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>209</v>
       </c>
@@ -6389,7 +6464,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>213</v>
       </c>
@@ -6412,7 +6487,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>216</v>
       </c>
@@ -6435,7 +6510,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>222</v>
       </c>
@@ -6458,7 +6533,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>225</v>
       </c>
@@ -6481,7 +6556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>228</v>
       </c>
@@ -6504,7 +6579,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>231</v>
       </c>
@@ -6525,7 +6600,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>1365</v>
       </c>
@@ -6546,7 +6621,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>237</v>
       </c>
@@ -6567,7 +6642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>220</v>
       </c>
@@ -6590,7 +6665,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>242</v>
       </c>
@@ -6611,7 +6686,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>246</v>
       </c>
@@ -6632,7 +6707,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>249</v>
       </c>
@@ -6653,7 +6728,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>253</v>
       </c>
@@ -6674,7 +6749,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>257</v>
       </c>
@@ -6695,7 +6770,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>261</v>
       </c>
@@ -6716,7 +6791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>265</v>
       </c>
@@ -6737,7 +6812,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>269</v>
       </c>
@@ -6758,7 +6833,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>273</v>
       </c>
@@ -6779,7 +6854,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>278</v>
       </c>
@@ -6800,7 +6875,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>280</v>
       </c>
@@ -6821,7 +6896,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>284</v>
       </c>
@@ -6842,7 +6917,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>828</v>
       </c>
@@ -6863,7 +6938,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>832</v>
       </c>
@@ -6884,7 +6959,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>836</v>
       </c>
@@ -6905,7 +6980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>840</v>
       </c>
@@ -6926,7 +7001,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>843</v>
       </c>
@@ -6947,7 +7022,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>847</v>
       </c>
@@ -6968,7 +7043,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>850</v>
       </c>
@@ -6989,7 +7064,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>286</v>
       </c>
@@ -7010,7 +7085,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>855</v>
       </c>
@@ -7031,7 +7106,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>869</v>
       </c>
@@ -7052,7 +7127,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>875</v>
       </c>
@@ -7073,7 +7148,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>892</v>
       </c>
@@ -7095,7 +7170,7 @@
       </c>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>1424</v>
       </c>
@@ -7116,7 +7191,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>899</v>
       </c>
@@ -7137,7 +7212,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>916</v>
       </c>
@@ -7158,7 +7233,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>1270</v>
       </c>
@@ -7179,7 +7254,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>923</v>
       </c>
@@ -7200,7 +7275,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>926</v>
       </c>
@@ -7221,7 +7296,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>928</v>
       </c>
@@ -7242,7 +7317,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>584</v>
       </c>
@@ -7263,7 +7338,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>948</v>
       </c>
@@ -7284,7 +7359,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>966</v>
       </c>
@@ -7305,7 +7380,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>969</v>
       </c>
@@ -7326,7 +7401,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>730</v>
       </c>
@@ -7347,7 +7422,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>976</v>
       </c>
@@ -7368,7 +7443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>983</v>
       </c>
@@ -7389,7 +7464,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>991</v>
       </c>
@@ -7410,7 +7485,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>995</v>
       </c>
@@ -7431,7 +7506,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>1011</v>
       </c>
@@ -7452,7 +7527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>1271</v>
       </c>
@@ -7473,7 +7548,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>1272</v>
       </c>
@@ -7494,7 +7569,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>1282</v>
       </c>
@@ -7515,7 +7590,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>52</v>
       </c>
@@ -7538,7 +7613,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>1325</v>
       </c>
@@ -7559,7 +7634,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>1321</v>
       </c>
@@ -7580,7 +7655,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>1343</v>
       </c>
@@ -7601,7 +7676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>850</v>
       </c>
@@ -7622,7 +7697,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>222</v>
       </c>
@@ -7643,7 +7718,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>1333</v>
       </c>
@@ -7664,7 +7739,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>822</v>
       </c>
@@ -7685,7 +7760,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>1344</v>
       </c>
@@ -7706,7 +7781,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>1353</v>
       </c>
@@ -7727,7 +7802,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>1355</v>
       </c>
@@ -7748,7 +7823,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>1358</v>
       </c>
@@ -7769,7 +7844,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>1395</v>
       </c>
@@ -7790,7 +7865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>1396</v>
       </c>
@@ -7811,7 +7886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>1397</v>
       </c>
@@ -7832,7 +7907,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>1406</v>
       </c>
@@ -7853,7 +7928,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>1410</v>
       </c>
@@ -7874,7 +7949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>1417</v>
       </c>
@@ -7895,7 +7970,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>1425</v>
       </c>
@@ -7916,7 +7991,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>1431</v>
       </c>
@@ -7937,7 +8012,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>1432</v>
       </c>
@@ -7958,7 +8033,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>1436</v>
       </c>
@@ -7979,7 +8054,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>1438</v>
       </c>
@@ -8000,7 +8075,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>780</v>
       </c>
@@ -8021,7 +8096,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>1453</v>
       </c>
@@ -8042,7 +8117,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>1456</v>
       </c>
@@ -8063,7 +8138,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>1460</v>
       </c>
@@ -8084,7 +8159,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>1471</v>
       </c>
@@ -8105,7 +8180,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>1485</v>
       </c>
@@ -8126,7 +8201,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>1488</v>
       </c>
@@ -8147,7 +8222,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>1491</v>
       </c>
@@ -8168,7 +8243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>1495</v>
       </c>
@@ -8189,7 +8264,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>1502</v>
       </c>
@@ -8210,7 +8285,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>1506</v>
       </c>
@@ -8231,7 +8306,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>1513</v>
       </c>
@@ -8252,7 +8327,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>1519</v>
       </c>
@@ -8273,7 +8348,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>326</v>
       </c>
@@ -8294,7 +8369,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>1529</v>
       </c>
@@ -8315,7 +8390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>1530</v>
       </c>
@@ -8336,7 +8411,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>1537</v>
       </c>
@@ -8357,7 +8432,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>1545</v>
       </c>
@@ -8380,7 +8455,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>1550</v>
       </c>
@@ -8401,7 +8476,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>1556</v>
       </c>
@@ -8422,7 +8497,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>1557</v>
       </c>
@@ -8443,7 +8518,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>1561</v>
       </c>
@@ -8464,7 +8539,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>1403</v>
       </c>
@@ -8485,26 +8560,108 @@
         <v>12</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>143</v>
+        <v>1569</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>144</v>
+        <v>1570</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>143</v>
+        <v>1569</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>145</v>
+        <v>1570</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F156" s="2" t="s">
-        <v>121</v>
-      </c>
+      <c r="F156" s="2"/>
       <c r="G156" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F157" s="2"/>
+      <c r="G157" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F158" s="2"/>
+      <c r="G158" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F159" s="2"/>
+      <c r="G159" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F160" s="2"/>
+      <c r="G160" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -8517,21 +8674,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I282"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I285"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="25.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="25.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="3"/>
+    <col min="7" max="7" width="23.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>288</v>
       </c>
@@ -8560,7 +8717,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>296</v>
       </c>
@@ -8585,7 +8742,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>302</v>
       </c>
@@ -8610,7 +8767,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>306</v>
       </c>
@@ -8635,7 +8792,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>309</v>
       </c>
@@ -8660,7 +8817,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>313</v>
       </c>
@@ -8685,7 +8842,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>317</v>
       </c>
@@ -8710,7 +8867,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>321</v>
       </c>
@@ -8735,7 +8892,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>325</v>
       </c>
@@ -8760,7 +8917,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>329</v>
       </c>
@@ -8785,7 +8942,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>331</v>
       </c>
@@ -8810,7 +8967,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>335</v>
       </c>
@@ -8835,7 +8992,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>338</v>
       </c>
@@ -8860,7 +9017,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>342</v>
       </c>
@@ -8885,7 +9042,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>346</v>
       </c>
@@ -8910,7 +9067,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>350</v>
       </c>
@@ -8935,7 +9092,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>352</v>
       </c>
@@ -8960,7 +9117,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>354</v>
       </c>
@@ -8985,7 +9142,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>356</v>
       </c>
@@ -9010,7 +9167,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>358</v>
       </c>
@@ -9035,7 +9192,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>360</v>
       </c>
@@ -9060,7 +9217,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>362</v>
       </c>
@@ -9085,7 +9242,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>363</v>
       </c>
@@ -9110,7 +9267,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>365</v>
       </c>
@@ -9135,7 +9292,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>367</v>
       </c>
@@ -9160,7 +9317,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>369</v>
       </c>
@@ -9185,7 +9342,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>372</v>
       </c>
@@ -9210,7 +9367,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>374</v>
       </c>
@@ -9239,7 +9396,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>380</v>
       </c>
@@ -9268,7 +9425,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>383</v>
       </c>
@@ -9297,7 +9454,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>386</v>
       </c>
@@ -9326,7 +9483,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>389</v>
       </c>
@@ -9355,7 +9512,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>391</v>
       </c>
@@ -9384,7 +9541,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>393</v>
       </c>
@@ -9413,7 +9570,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>395</v>
       </c>
@@ -9442,7 +9599,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>399</v>
       </c>
@@ -9471,7 +9628,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>402</v>
       </c>
@@ -9500,7 +9657,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>404</v>
       </c>
@@ -9529,7 +9686,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>406</v>
       </c>
@@ -9558,7 +9715,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>408</v>
       </c>
@@ -9587,7 +9744,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>411</v>
       </c>
@@ -9616,7 +9773,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>413</v>
       </c>
@@ -9645,7 +9802,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>416</v>
       </c>
@@ -9674,7 +9831,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>419</v>
       </c>
@@ -9703,7 +9860,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>421</v>
       </c>
@@ -9732,7 +9889,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>424</v>
       </c>
@@ -9761,7 +9918,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>426</v>
       </c>
@@ -9790,7 +9947,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>429</v>
       </c>
@@ -9819,7 +9976,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>432</v>
       </c>
@@ -9848,7 +10005,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>435</v>
       </c>
@@ -9877,7 +10034,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>439</v>
       </c>
@@ -9906,7 +10063,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>442</v>
       </c>
@@ -9935,7 +10092,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>445</v>
       </c>
@@ -9964,7 +10121,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>448</v>
       </c>
@@ -9993,7 +10150,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>452</v>
       </c>
@@ -10022,7 +10179,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>455</v>
       </c>
@@ -10051,7 +10208,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>457</v>
       </c>
@@ -10080,7 +10237,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>459</v>
       </c>
@@ -10109,7 +10266,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>461</v>
       </c>
@@ -10138,7 +10295,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>463</v>
       </c>
@@ -10167,7 +10324,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>465</v>
       </c>
@@ -10196,7 +10353,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>467</v>
       </c>
@@ -10225,7 +10382,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>469</v>
       </c>
@@ -10254,7 +10411,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>470</v>
       </c>
@@ -10283,7 +10440,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>473</v>
       </c>
@@ -10312,7 +10469,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>475</v>
       </c>
@@ -10341,7 +10498,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>477</v>
       </c>
@@ -10370,7 +10527,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>479</v>
       </c>
@@ -10399,7 +10556,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>483</v>
       </c>
@@ -10428,7 +10585,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>485</v>
       </c>
@@ -10457,7 +10614,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>487</v>
       </c>
@@ -10486,7 +10643,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>489</v>
       </c>
@@ -10515,7 +10672,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>491</v>
       </c>
@@ -10544,7 +10701,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>494</v>
       </c>
@@ -10573,7 +10730,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>496</v>
       </c>
@@ -10602,7 +10759,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>499</v>
       </c>
@@ -10631,7 +10788,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>501</v>
       </c>
@@ -10660,7 +10817,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>503</v>
       </c>
@@ -10689,7 +10846,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>505</v>
       </c>
@@ -10714,7 +10871,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>508</v>
       </c>
@@ -10739,7 +10896,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>510</v>
       </c>
@@ -10764,7 +10921,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>512</v>
       </c>
@@ -10789,7 +10946,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>513</v>
       </c>
@@ -10814,7 +10971,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>515</v>
       </c>
@@ -10839,7 +10996,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>517</v>
       </c>
@@ -10864,7 +11021,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>521</v>
       </c>
@@ -10889,7 +11046,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>523</v>
       </c>
@@ -10914,7 +11071,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>527</v>
       </c>
@@ -10939,7 +11096,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>535</v>
       </c>
@@ -10964,7 +11121,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>539</v>
       </c>
@@ -10989,7 +11146,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>541</v>
       </c>
@@ -11014,7 +11171,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>545</v>
       </c>
@@ -11039,7 +11196,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>549</v>
       </c>
@@ -11064,7 +11221,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>551</v>
       </c>
@@ -11089,7 +11246,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>555</v>
       </c>
@@ -11114,7 +11271,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>560</v>
       </c>
@@ -11139,7 +11296,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>564</v>
       </c>
@@ -11164,7 +11321,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>568</v>
       </c>
@@ -11189,7 +11346,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>570</v>
       </c>
@@ -11214,7 +11371,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>573</v>
       </c>
@@ -11239,7 +11396,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>576</v>
       </c>
@@ -11264,7 +11421,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>581</v>
       </c>
@@ -11289,7 +11446,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>583</v>
       </c>
@@ -11314,7 +11471,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>587</v>
       </c>
@@ -11339,7 +11496,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>589</v>
       </c>
@@ -11364,7 +11521,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>593</v>
       </c>
@@ -11389,7 +11546,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>595</v>
       </c>
@@ -11414,7 +11571,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>599</v>
       </c>
@@ -11439,7 +11596,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>603</v>
       </c>
@@ -11464,7 +11621,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>607</v>
       </c>
@@ -11489,7 +11646,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>609</v>
       </c>
@@ -11514,7 +11671,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>613</v>
       </c>
@@ -11539,7 +11696,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>615</v>
       </c>
@@ -11564,7 +11721,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>619</v>
       </c>
@@ -11589,7 +11746,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>623</v>
       </c>
@@ -11618,7 +11775,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>624</v>
       </c>
@@ -11647,7 +11804,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>626</v>
       </c>
@@ -11676,7 +11833,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>629</v>
       </c>
@@ -11701,7 +11858,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>633</v>
       </c>
@@ -11726,7 +11883,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>635</v>
       </c>
@@ -11755,7 +11912,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>638</v>
       </c>
@@ -11784,7 +11941,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>640</v>
       </c>
@@ -11809,7 +11966,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>644</v>
       </c>
@@ -11838,7 +11995,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>646</v>
       </c>
@@ -11867,7 +12024,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>648</v>
       </c>
@@ -11896,7 +12053,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>650</v>
       </c>
@@ -11925,7 +12082,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>652</v>
       </c>
@@ -11954,7 +12111,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>654</v>
       </c>
@@ -11979,7 +12136,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>656</v>
       </c>
@@ -12004,7 +12161,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>658</v>
       </c>
@@ -12033,7 +12190,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>660</v>
       </c>
@@ -12058,7 +12215,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>662</v>
       </c>
@@ -12083,7 +12240,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>665</v>
       </c>
@@ -12112,7 +12269,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>667</v>
       </c>
@@ -12137,7 +12294,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>668</v>
       </c>
@@ -12166,7 +12323,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>670</v>
       </c>
@@ -12191,7 +12348,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>674</v>
       </c>
@@ -12216,7 +12373,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>678</v>
       </c>
@@ -12241,7 +12398,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>680</v>
       </c>
@@ -12266,7 +12423,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>684</v>
       </c>
@@ -12295,7 +12452,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>686</v>
       </c>
@@ -12320,7 +12477,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>690</v>
       </c>
@@ -12349,7 +12506,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>692</v>
       </c>
@@ -12378,7 +12535,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>695</v>
       </c>
@@ -12407,7 +12564,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>137</v>
       </c>
@@ -12432,7 +12589,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>699</v>
       </c>
@@ -12457,7 +12614,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>702</v>
       </c>
@@ -12482,7 +12639,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>705</v>
       </c>
@@ -12507,7 +12664,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>706</v>
       </c>
@@ -12532,7 +12689,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>708</v>
       </c>
@@ -12557,7 +12714,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>709</v>
       </c>
@@ -12586,7 +12743,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>710</v>
       </c>
@@ -12611,7 +12768,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>714</v>
       </c>
@@ -12636,7 +12793,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>716</v>
       </c>
@@ -12661,7 +12818,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>718</v>
       </c>
@@ -12686,7 +12843,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>720</v>
       </c>
@@ -12711,7 +12868,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>722</v>
       </c>
@@ -12736,7 +12893,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>724</v>
       </c>
@@ -12765,7 +12922,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>726</v>
       </c>
@@ -12790,7 +12947,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>728</v>
       </c>
@@ -12815,7 +12972,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>730</v>
       </c>
@@ -12840,7 +12997,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>732</v>
       </c>
@@ -12865,7 +13022,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>734</v>
       </c>
@@ -12894,7 +13051,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>736</v>
       </c>
@@ -12923,7 +13080,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>738</v>
       </c>
@@ -12952,7 +13109,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>740</v>
       </c>
@@ -12981,7 +13138,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>742</v>
       </c>
@@ -13010,7 +13167,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>744</v>
       </c>
@@ -13035,7 +13192,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>748</v>
       </c>
@@ -13064,7 +13221,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>750</v>
       </c>
@@ -13089,7 +13246,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>753</v>
       </c>
@@ -13114,7 +13271,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>757</v>
       </c>
@@ -13139,7 +13296,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>759</v>
       </c>
@@ -13164,7 +13321,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>763</v>
       </c>
@@ -13193,7 +13350,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>765</v>
       </c>
@@ -13218,7 +13375,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>769</v>
       </c>
@@ -13243,7 +13400,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>773</v>
       </c>
@@ -13268,7 +13425,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>777</v>
       </c>
@@ -13293,7 +13450,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>779</v>
       </c>
@@ -13318,7 +13475,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>783</v>
       </c>
@@ -13343,7 +13500,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>785</v>
       </c>
@@ -13368,7 +13525,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>787</v>
       </c>
@@ -13393,7 +13550,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>789</v>
       </c>
@@ -13418,7 +13575,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>791</v>
       </c>
@@ -13443,7 +13600,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>793</v>
       </c>
@@ -13468,7 +13625,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>797</v>
       </c>
@@ -13493,7 +13650,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>799</v>
       </c>
@@ -13518,7 +13675,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>801</v>
       </c>
@@ -13543,7 +13700,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>803</v>
       </c>
@@ -13568,7 +13725,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>805</v>
       </c>
@@ -13593,7 +13750,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>807</v>
       </c>
@@ -13618,7 +13775,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>809</v>
       </c>
@@ -13643,7 +13800,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>811</v>
       </c>
@@ -13668,7 +13825,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>813</v>
       </c>
@@ -13693,7 +13850,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>819</v>
       </c>
@@ -13718,7 +13875,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>820</v>
       </c>
@@ -13743,7 +13900,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>821</v>
       </c>
@@ -13768,7 +13925,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>859</v>
       </c>
@@ -13793,7 +13950,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>861</v>
       </c>
@@ -13818,7 +13975,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>865</v>
       </c>
@@ -13843,7 +14000,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>873</v>
       </c>
@@ -13868,7 +14025,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>878</v>
       </c>
@@ -13893,7 +14050,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>879</v>
       </c>
@@ -13918,7 +14075,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>880</v>
       </c>
@@ -13943,7 +14100,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>881</v>
       </c>
@@ -13968,7 +14125,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>882</v>
       </c>
@@ -13993,7 +14150,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>896</v>
       </c>
@@ -14018,7 +14175,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>904</v>
       </c>
@@ -14043,7 +14200,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>906</v>
       </c>
@@ -14068,7 +14225,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>908</v>
       </c>
@@ -14097,7 +14254,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>910</v>
       </c>
@@ -14126,7 +14283,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>912</v>
       </c>
@@ -14155,7 +14312,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>915</v>
       </c>
@@ -14184,7 +14341,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>932</v>
       </c>
@@ -14209,7 +14366,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>933</v>
       </c>
@@ -14234,7 +14391,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>943</v>
       </c>
@@ -14259,7 +14416,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>944</v>
       </c>
@@ -14284,7 +14441,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>952</v>
       </c>
@@ -14309,7 +14466,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>953</v>
       </c>
@@ -14334,7 +14491,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>195</v>
       </c>
@@ -14363,7 +14520,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>959</v>
       </c>
@@ -14388,7 +14545,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>962</v>
       </c>
@@ -14413,7 +14570,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>974</v>
       </c>
@@ -14438,7 +14595,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>980</v>
       </c>
@@ -14463,7 +14620,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>987</v>
       </c>
@@ -14488,7 +14645,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>989</v>
       </c>
@@ -14517,7 +14674,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>999</v>
       </c>
@@ -14542,7 +14699,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>1003</v>
       </c>
@@ -14567,7 +14724,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>1012</v>
       </c>
@@ -14592,7 +14749,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>1247</v>
       </c>
@@ -14617,7 +14774,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>1250</v>
       </c>
@@ -14642,7 +14799,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>1253</v>
       </c>
@@ -14667,7 +14824,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>1256</v>
       </c>
@@ -14692,7 +14849,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>1259</v>
       </c>
@@ -14717,7 +14874,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>1262</v>
       </c>
@@ -14742,7 +14899,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>1267</v>
       </c>
@@ -14767,7 +14924,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>1278</v>
       </c>
@@ -14792,7 +14949,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>1283</v>
       </c>
@@ -14817,7 +14974,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>1003</v>
       </c>
@@ -14842,7 +14999,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>732</v>
       </c>
@@ -14867,7 +15024,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>631</v>
       </c>
@@ -14892,7 +15049,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>1289</v>
       </c>
@@ -14921,7 +15078,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>531</v>
       </c>
@@ -14946,7 +15103,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>1305</v>
       </c>
@@ -14971,7 +15128,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>1307</v>
       </c>
@@ -14996,7 +15153,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>1309</v>
       </c>
@@ -15021,7 +15178,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>1311</v>
       </c>
@@ -15046,7 +15203,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>1312</v>
       </c>
@@ -15071,7 +15228,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>1314</v>
       </c>
@@ -15096,7 +15253,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>1316</v>
       </c>
@@ -15121,7 +15278,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>1318</v>
       </c>
@@ -15146,7 +15303,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>1337</v>
       </c>
@@ -15175,7 +15332,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>1346</v>
       </c>
@@ -15200,7 +15357,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>1347</v>
       </c>
@@ -15229,7 +15386,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>1362</v>
       </c>
@@ -15258,7 +15415,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>1366</v>
       </c>
@@ -15283,7 +15440,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>1367</v>
       </c>
@@ -15308,7 +15465,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>1368</v>
       </c>
@@ -15333,7 +15490,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>1369</v>
       </c>
@@ -15358,7 +15515,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>1370</v>
       </c>
@@ -15383,7 +15540,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>1371</v>
       </c>
@@ -15408,7 +15565,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>1372</v>
       </c>
@@ -15433,7 +15590,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>1374</v>
       </c>
@@ -15458,7 +15615,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>1373</v>
       </c>
@@ -15483,7 +15640,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>1414</v>
       </c>
@@ -15508,7 +15665,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>1421</v>
       </c>
@@ -15533,7 +15690,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>1442</v>
       </c>
@@ -15558,7 +15715,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>1448</v>
       </c>
@@ -15583,7 +15740,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>1465</v>
       </c>
@@ -15608,7 +15765,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>1468</v>
       </c>
@@ -15633,7 +15790,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>1474</v>
       </c>
@@ -15658,7 +15815,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>1479</v>
       </c>
@@ -15683,7 +15840,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>1482</v>
       </c>
@@ -15712,7 +15869,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>1499</v>
       </c>
@@ -15737,7 +15894,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>1510</v>
       </c>
@@ -15766,7 +15923,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>1516</v>
       </c>
@@ -15795,7 +15952,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>1525</v>
       </c>
@@ -15820,7 +15977,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>1534</v>
       </c>
@@ -15849,7 +16006,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>1539</v>
       </c>
@@ -15874,7 +16031,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>1542</v>
       </c>
@@ -15899,7 +16056,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>1551</v>
       </c>
@@ -15924,7 +16081,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>1565</v>
       </c>
@@ -15949,8 +16106,83 @@
         <v>1566</v>
       </c>
     </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="F283" s="2"/>
+      <c r="G283" s="2"/>
+      <c r="H283" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="I283" s="2" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="F284" s="2"/>
+      <c r="G284" s="2"/>
+      <c r="H284" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="I284" s="2" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" s="2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>1592</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E285" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="F285" s="2"/>
+      <c r="G285" s="2"/>
+      <c r="H285" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="I285" s="2" t="s">
+        <v>1593</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I281"/>
+  <autoFilter ref="A1:I285"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/referências.xlsx
+++ b/referências.xlsx
@@ -16,7 +16,7 @@
     <sheet name="destinos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">destinos!$A$1:$I$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">destinos!$A$1:$I$286</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">operador!$A$1:$G$156</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3196" uniqueCount="1594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3240" uniqueCount="1614">
   <si>
     <t>Iata Code</t>
   </si>
@@ -4822,6 +4822,66 @@
   </si>
   <si>
     <t>EGSS</t>
+  </si>
+  <si>
+    <t>YYC</t>
+  </si>
+  <si>
+    <t>Calgary</t>
+  </si>
+  <si>
+    <t>CYYC</t>
+  </si>
+  <si>
+    <t>NSI</t>
+  </si>
+  <si>
+    <t>FKYS</t>
+  </si>
+  <si>
+    <t>Yaoundé</t>
+  </si>
+  <si>
+    <t>CMA</t>
+  </si>
+  <si>
+    <t>2C</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>CMA CGM AIR CARGO</t>
+  </si>
+  <si>
+    <t>HQ</t>
+  </si>
+  <si>
+    <t>Compass Cargo</t>
+  </si>
+  <si>
+    <t>ADZ</t>
+  </si>
+  <si>
+    <t>Compass Cargo Airlines LTD</t>
+  </si>
+  <si>
+    <t>MEA</t>
+  </si>
+  <si>
+    <t>ROO</t>
+  </si>
+  <si>
+    <t>Macaé</t>
+  </si>
+  <si>
+    <t>Rondonópolis</t>
+  </si>
+  <si>
+    <t>SBRD</t>
+  </si>
+  <si>
+    <t>SBME</t>
   </si>
 </sst>
 </file>
@@ -5177,20 +5237,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H160"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H162"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="67.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="3"/>
+    <col min="1" max="1" width="15.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="67.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5213,7 +5273,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -5236,7 +5296,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -5259,7 +5319,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -5282,7 +5342,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -5305,7 +5365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -5328,7 +5388,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
@@ -5351,7 +5411,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -5374,7 +5434,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
@@ -5397,7 +5457,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
@@ -5420,7 +5480,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>46</v>
       </c>
@@ -5443,7 +5503,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>49</v>
       </c>
@@ -5466,7 +5526,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>53</v>
       </c>
@@ -5489,7 +5549,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>57</v>
       </c>
@@ -5512,7 +5572,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>60</v>
       </c>
@@ -5535,7 +5595,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>64</v>
       </c>
@@ -5558,7 +5618,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>68</v>
       </c>
@@ -5581,7 +5641,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>72</v>
       </c>
@@ -5604,7 +5664,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>76</v>
       </c>
@@ -5627,7 +5687,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>80</v>
       </c>
@@ -5650,7 +5710,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>84</v>
       </c>
@@ -5671,7 +5731,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>88</v>
       </c>
@@ -5694,7 +5754,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>92</v>
       </c>
@@ -5717,7 +5777,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>95</v>
       </c>
@@ -5740,7 +5800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>98</v>
       </c>
@@ -5761,7 +5821,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>102</v>
       </c>
@@ -5784,7 +5844,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>104</v>
       </c>
@@ -5807,7 +5867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>107</v>
       </c>
@@ -5830,7 +5890,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>110</v>
       </c>
@@ -5853,7 +5913,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>113</v>
       </c>
@@ -5876,7 +5936,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>117</v>
       </c>
@@ -5899,7 +5959,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>122</v>
       </c>
@@ -5922,7 +5982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>126</v>
       </c>
@@ -5945,7 +6005,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>129</v>
       </c>
@@ -5968,7 +6028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>133</v>
       </c>
@@ -5991,7 +6051,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>137</v>
       </c>
@@ -6014,7 +6074,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>139</v>
       </c>
@@ -6035,7 +6095,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>146</v>
       </c>
@@ -6058,7 +6118,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>150</v>
       </c>
@@ -6081,7 +6141,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>153</v>
       </c>
@@ -6104,7 +6164,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>157</v>
       </c>
@@ -6127,7 +6187,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>160</v>
       </c>
@@ -6150,7 +6210,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>163</v>
       </c>
@@ -6171,7 +6231,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>167</v>
       </c>
@@ -6194,7 +6254,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>815</v>
       </c>
@@ -6217,7 +6277,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>173</v>
       </c>
@@ -6240,7 +6300,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>175</v>
       </c>
@@ -6263,7 +6323,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>179</v>
       </c>
@@ -6286,7 +6346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>183</v>
       </c>
@@ -6309,7 +6369,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>186</v>
       </c>
@@ -6330,7 +6390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>190</v>
       </c>
@@ -6351,7 +6411,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>193</v>
       </c>
@@ -6374,7 +6434,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>197</v>
       </c>
@@ -6395,7 +6455,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>201</v>
       </c>
@@ -6418,7 +6478,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>205</v>
       </c>
@@ -6441,7 +6501,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>209</v>
       </c>
@@ -6464,7 +6524,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>213</v>
       </c>
@@ -6487,7 +6547,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>216</v>
       </c>
@@ -6510,7 +6570,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>222</v>
       </c>
@@ -6533,7 +6593,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>225</v>
       </c>
@@ -6556,7 +6616,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>228</v>
       </c>
@@ -6579,7 +6639,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>231</v>
       </c>
@@ -6600,7 +6660,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>1365</v>
       </c>
@@ -6621,7 +6681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>237</v>
       </c>
@@ -6642,7 +6702,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>220</v>
       </c>
@@ -6665,7 +6725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>242</v>
       </c>
@@ -6686,7 +6746,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>246</v>
       </c>
@@ -6707,7 +6767,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>249</v>
       </c>
@@ -6728,7 +6788,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>253</v>
       </c>
@@ -6749,7 +6809,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>257</v>
       </c>
@@ -6770,7 +6830,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>261</v>
       </c>
@@ -6791,7 +6851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>265</v>
       </c>
@@ -6812,7 +6872,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>269</v>
       </c>
@@ -6833,7 +6893,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>273</v>
       </c>
@@ -6854,7 +6914,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>278</v>
       </c>
@@ -6875,7 +6935,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>280</v>
       </c>
@@ -6896,7 +6956,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>284</v>
       </c>
@@ -6917,7 +6977,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>828</v>
       </c>
@@ -6938,7 +6998,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>832</v>
       </c>
@@ -6959,7 +7019,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>836</v>
       </c>
@@ -6980,7 +7040,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>840</v>
       </c>
@@ -7001,7 +7061,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>843</v>
       </c>
@@ -7022,7 +7082,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>847</v>
       </c>
@@ -7043,7 +7103,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>850</v>
       </c>
@@ -7064,7 +7124,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>286</v>
       </c>
@@ -7085,7 +7145,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>855</v>
       </c>
@@ -7106,7 +7166,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>869</v>
       </c>
@@ -7127,7 +7187,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>875</v>
       </c>
@@ -7148,7 +7208,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>892</v>
       </c>
@@ -7170,7 +7230,7 @@
       </c>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>1424</v>
       </c>
@@ -7191,7 +7251,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>899</v>
       </c>
@@ -7212,7 +7272,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>916</v>
       </c>
@@ -7233,7 +7293,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>1270</v>
       </c>
@@ -7254,7 +7314,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>923</v>
       </c>
@@ -7275,7 +7335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>926</v>
       </c>
@@ -7296,7 +7356,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>928</v>
       </c>
@@ -7317,7 +7377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>584</v>
       </c>
@@ -7338,7 +7398,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>948</v>
       </c>
@@ -7359,7 +7419,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>966</v>
       </c>
@@ -7380,7 +7440,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>969</v>
       </c>
@@ -7401,7 +7461,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>730</v>
       </c>
@@ -7422,7 +7482,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>976</v>
       </c>
@@ -7443,7 +7503,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>983</v>
       </c>
@@ -7464,7 +7524,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>991</v>
       </c>
@@ -7485,7 +7545,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>995</v>
       </c>
@@ -7506,7 +7566,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>1011</v>
       </c>
@@ -7527,7 +7587,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>1271</v>
       </c>
@@ -7548,7 +7608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>1272</v>
       </c>
@@ -7569,7 +7629,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>1282</v>
       </c>
@@ -7590,7 +7650,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>52</v>
       </c>
@@ -7613,7 +7673,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>1325</v>
       </c>
@@ -7634,7 +7694,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>1321</v>
       </c>
@@ -7655,7 +7715,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>1343</v>
       </c>
@@ -7676,7 +7736,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>850</v>
       </c>
@@ -7697,7 +7757,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>222</v>
       </c>
@@ -7718,7 +7778,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>1333</v>
       </c>
@@ -7739,7 +7799,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>822</v>
       </c>
@@ -7760,7 +7820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>1344</v>
       </c>
@@ -7781,7 +7841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>1353</v>
       </c>
@@ -7802,7 +7862,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>1355</v>
       </c>
@@ -7823,7 +7883,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>1358</v>
       </c>
@@ -7844,7 +7904,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>1395</v>
       </c>
@@ -7865,7 +7925,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>1396</v>
       </c>
@@ -7886,7 +7946,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>1397</v>
       </c>
@@ -7907,7 +7967,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>1406</v>
       </c>
@@ -7928,7 +7988,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>1410</v>
       </c>
@@ -7949,7 +8009,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>1417</v>
       </c>
@@ -7970,7 +8030,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>1425</v>
       </c>
@@ -7991,7 +8051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>1431</v>
       </c>
@@ -8012,7 +8072,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>1432</v>
       </c>
@@ -8033,7 +8093,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>1436</v>
       </c>
@@ -8054,7 +8114,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>1438</v>
       </c>
@@ -8075,7 +8135,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>780</v>
       </c>
@@ -8096,7 +8156,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>1453</v>
       </c>
@@ -8117,7 +8177,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>1456</v>
       </c>
@@ -8138,7 +8198,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>1460</v>
       </c>
@@ -8159,7 +8219,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>1471</v>
       </c>
@@ -8180,7 +8240,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>1485</v>
       </c>
@@ -8201,7 +8261,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>1488</v>
       </c>
@@ -8222,7 +8282,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>1491</v>
       </c>
@@ -8243,7 +8303,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>1495</v>
       </c>
@@ -8264,7 +8324,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>1502</v>
       </c>
@@ -8285,7 +8345,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>1506</v>
       </c>
@@ -8306,7 +8366,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>1513</v>
       </c>
@@ -8327,7 +8387,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>1519</v>
       </c>
@@ -8348,7 +8408,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>326</v>
       </c>
@@ -8369,7 +8429,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>1529</v>
       </c>
@@ -8390,7 +8450,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
         <v>1530</v>
       </c>
@@ -8411,7 +8471,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>1537</v>
       </c>
@@ -8432,7 +8492,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>1545</v>
       </c>
@@ -8455,7 +8515,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>1550</v>
       </c>
@@ -8476,7 +8536,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>1556</v>
       </c>
@@ -8497,7 +8557,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
         <v>1557</v>
       </c>
@@ -8518,7 +8578,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
         <v>1561</v>
       </c>
@@ -8539,7 +8599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
         <v>1403</v>
       </c>
@@ -8560,7 +8620,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
         <v>1569</v>
       </c>
@@ -8581,7 +8641,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
         <v>1571</v>
       </c>
@@ -8602,7 +8662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
         <v>1575</v>
       </c>
@@ -8623,7 +8683,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
         <v>1584</v>
       </c>
@@ -8644,7 +8704,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
         <v>1588</v>
       </c>
@@ -8662,6 +8722,48 @@
       </c>
       <c r="F160" s="2"/>
       <c r="G160" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F161" s="2"/>
+      <c r="G161" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F162" s="2"/>
+      <c r="G162" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -8674,21 +8776,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I285"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I289"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="25.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="25.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="3"/>
+    <col min="7" max="7" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>288</v>
       </c>
@@ -8717,7 +8819,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>296</v>
       </c>
@@ -8742,7 +8844,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>302</v>
       </c>
@@ -8767,7 +8869,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>306</v>
       </c>
@@ -8792,7 +8894,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>309</v>
       </c>
@@ -8817,7 +8919,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>313</v>
       </c>
@@ -8842,7 +8944,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>317</v>
       </c>
@@ -8867,7 +8969,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>321</v>
       </c>
@@ -8892,7 +8994,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>325</v>
       </c>
@@ -8917,7 +9019,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>329</v>
       </c>
@@ -8942,7 +9044,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>331</v>
       </c>
@@ -8967,7 +9069,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>335</v>
       </c>
@@ -8992,7 +9094,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>338</v>
       </c>
@@ -9017,7 +9119,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>342</v>
       </c>
@@ -9042,7 +9144,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>346</v>
       </c>
@@ -9067,7 +9169,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>350</v>
       </c>
@@ -9092,7 +9194,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>352</v>
       </c>
@@ -9117,7 +9219,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>354</v>
       </c>
@@ -9142,7 +9244,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>356</v>
       </c>
@@ -9167,7 +9269,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>358</v>
       </c>
@@ -9192,7 +9294,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>360</v>
       </c>
@@ -9217,7 +9319,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>362</v>
       </c>
@@ -9242,7 +9344,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>363</v>
       </c>
@@ -9267,7 +9369,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>365</v>
       </c>
@@ -9292,7 +9394,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>367</v>
       </c>
@@ -9317,7 +9419,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>369</v>
       </c>
@@ -9342,7 +9444,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>372</v>
       </c>
@@ -9367,7 +9469,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>374</v>
       </c>
@@ -9396,7 +9498,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>380</v>
       </c>
@@ -9425,7 +9527,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>383</v>
       </c>
@@ -9454,7 +9556,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>386</v>
       </c>
@@ -9483,7 +9585,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>389</v>
       </c>
@@ -9512,7 +9614,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>391</v>
       </c>
@@ -9541,7 +9643,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>393</v>
       </c>
@@ -9570,7 +9672,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>395</v>
       </c>
@@ -9599,7 +9701,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>399</v>
       </c>
@@ -9628,7 +9730,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>402</v>
       </c>
@@ -9657,7 +9759,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>404</v>
       </c>
@@ -9686,7 +9788,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>406</v>
       </c>
@@ -9715,7 +9817,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>408</v>
       </c>
@@ -9744,7 +9846,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>411</v>
       </c>
@@ -9773,7 +9875,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>413</v>
       </c>
@@ -9802,7 +9904,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>416</v>
       </c>
@@ -9831,7 +9933,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>419</v>
       </c>
@@ -9860,7 +9962,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>421</v>
       </c>
@@ -9889,7 +9991,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>424</v>
       </c>
@@ -9918,7 +10020,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>426</v>
       </c>
@@ -9947,7 +10049,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>429</v>
       </c>
@@ -9976,7 +10078,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>432</v>
       </c>
@@ -10005,7 +10107,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>435</v>
       </c>
@@ -10034,7 +10136,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>439</v>
       </c>
@@ -10063,7 +10165,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>442</v>
       </c>
@@ -10092,7 +10194,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>445</v>
       </c>
@@ -10121,7 +10223,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>448</v>
       </c>
@@ -10150,7 +10252,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>452</v>
       </c>
@@ -10179,7 +10281,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>455</v>
       </c>
@@ -10208,7 +10310,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>457</v>
       </c>
@@ -10237,7 +10339,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>459</v>
       </c>
@@ -10266,7 +10368,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>461</v>
       </c>
@@ -10295,7 +10397,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>463</v>
       </c>
@@ -10324,7 +10426,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>465</v>
       </c>
@@ -10353,7 +10455,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>467</v>
       </c>
@@ -10382,7 +10484,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>469</v>
       </c>
@@ -10411,7 +10513,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>470</v>
       </c>
@@ -10440,7 +10542,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>473</v>
       </c>
@@ -10469,7 +10571,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>475</v>
       </c>
@@ -10498,7 +10600,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>477</v>
       </c>
@@ -10527,7 +10629,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>479</v>
       </c>
@@ -10556,7 +10658,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>483</v>
       </c>
@@ -10585,7 +10687,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>485</v>
       </c>
@@ -10614,7 +10716,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>487</v>
       </c>
@@ -10643,7 +10745,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>489</v>
       </c>
@@ -10672,7 +10774,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>491</v>
       </c>
@@ -10701,7 +10803,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>494</v>
       </c>
@@ -10730,7 +10832,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>496</v>
       </c>
@@ -10759,7 +10861,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>499</v>
       </c>
@@ -10788,7 +10890,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>501</v>
       </c>
@@ -10817,7 +10919,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>503</v>
       </c>
@@ -10846,7 +10948,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>505</v>
       </c>
@@ -10871,7 +10973,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>508</v>
       </c>
@@ -10896,7 +10998,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>510</v>
       </c>
@@ -10921,7 +11023,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>512</v>
       </c>
@@ -10946,7 +11048,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>513</v>
       </c>
@@ -10971,7 +11073,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>515</v>
       </c>
@@ -10996,7 +11098,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>517</v>
       </c>
@@ -11021,7 +11123,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>521</v>
       </c>
@@ -11046,7 +11148,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>523</v>
       </c>
@@ -11071,7 +11173,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>527</v>
       </c>
@@ -11096,7 +11198,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>535</v>
       </c>
@@ -11121,7 +11223,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>539</v>
       </c>
@@ -11146,7 +11248,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>541</v>
       </c>
@@ -11171,7 +11273,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>545</v>
       </c>
@@ -11196,7 +11298,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>549</v>
       </c>
@@ -11221,7 +11323,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>551</v>
       </c>
@@ -11246,7 +11348,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>555</v>
       </c>
@@ -11271,7 +11373,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>560</v>
       </c>
@@ -11296,7 +11398,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>564</v>
       </c>
@@ -11321,7 +11423,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>568</v>
       </c>
@@ -11346,7 +11448,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>570</v>
       </c>
@@ -11371,7 +11473,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>573</v>
       </c>
@@ -11396,7 +11498,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>576</v>
       </c>
@@ -11421,7 +11523,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>581</v>
       </c>
@@ -11446,7 +11548,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>583</v>
       </c>
@@ -11471,7 +11573,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>587</v>
       </c>
@@ -11496,7 +11598,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>589</v>
       </c>
@@ -11521,7 +11623,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>593</v>
       </c>
@@ -11546,7 +11648,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>595</v>
       </c>
@@ -11571,7 +11673,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>599</v>
       </c>
@@ -11596,7 +11698,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>603</v>
       </c>
@@ -11621,7 +11723,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>607</v>
       </c>
@@ -11646,7 +11748,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>609</v>
       </c>
@@ -11671,7 +11773,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>613</v>
       </c>
@@ -11696,7 +11798,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>615</v>
       </c>
@@ -11721,7 +11823,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>619</v>
       </c>
@@ -11746,7 +11848,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>623</v>
       </c>
@@ -11775,7 +11877,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>624</v>
       </c>
@@ -11804,7 +11906,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>626</v>
       </c>
@@ -11833,7 +11935,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>629</v>
       </c>
@@ -11858,7 +11960,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>633</v>
       </c>
@@ -11883,7 +11985,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>635</v>
       </c>
@@ -11912,7 +12014,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>638</v>
       </c>
@@ -11941,7 +12043,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>640</v>
       </c>
@@ -11966,7 +12068,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>644</v>
       </c>
@@ -11995,7 +12097,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>646</v>
       </c>
@@ -12024,7 +12126,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>648</v>
       </c>
@@ -12053,7 +12155,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>650</v>
       </c>
@@ -12082,7 +12184,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>652</v>
       </c>
@@ -12111,7 +12213,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>654</v>
       </c>
@@ -12136,7 +12238,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>656</v>
       </c>
@@ -12161,7 +12263,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>658</v>
       </c>
@@ -12190,7 +12292,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>660</v>
       </c>
@@ -12215,7 +12317,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>662</v>
       </c>
@@ -12240,7 +12342,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>665</v>
       </c>
@@ -12269,7 +12371,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>667</v>
       </c>
@@ -12294,7 +12396,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>668</v>
       </c>
@@ -12323,7 +12425,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>670</v>
       </c>
@@ -12348,7 +12450,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>674</v>
       </c>
@@ -12373,7 +12475,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>678</v>
       </c>
@@ -12398,7 +12500,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>680</v>
       </c>
@@ -12423,7 +12525,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>684</v>
       </c>
@@ -12452,7 +12554,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>686</v>
       </c>
@@ -12477,7 +12579,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>690</v>
       </c>
@@ -12506,7 +12608,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>692</v>
       </c>
@@ -12535,7 +12637,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>695</v>
       </c>
@@ -12564,7 +12666,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>137</v>
       </c>
@@ -12589,7 +12691,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>699</v>
       </c>
@@ -12614,7 +12716,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>702</v>
       </c>
@@ -12639,7 +12741,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
         <v>705</v>
       </c>
@@ -12664,7 +12766,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>706</v>
       </c>
@@ -12689,7 +12791,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>708</v>
       </c>
@@ -12714,7 +12816,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>709</v>
       </c>
@@ -12743,7 +12845,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>710</v>
       </c>
@@ -12768,7 +12870,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
         <v>714</v>
       </c>
@@ -12793,7 +12895,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
         <v>716</v>
       </c>
@@ -12818,7 +12920,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
         <v>718</v>
       </c>
@@ -12843,7 +12945,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
         <v>720</v>
       </c>
@@ -12868,7 +12970,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
         <v>722</v>
       </c>
@@ -12893,7 +12995,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
         <v>724</v>
       </c>
@@ -12922,7 +13024,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
         <v>726</v>
       </c>
@@ -12947,7 +13049,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
         <v>728</v>
       </c>
@@ -12972,7 +13074,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
         <v>730</v>
       </c>
@@ -12997,7 +13099,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
         <v>732</v>
       </c>
@@ -13022,7 +13124,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
         <v>734</v>
       </c>
@@ -13051,7 +13153,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
         <v>736</v>
       </c>
@@ -13080,7 +13182,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
         <v>738</v>
       </c>
@@ -13109,7 +13211,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
         <v>740</v>
       </c>
@@ -13138,7 +13240,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
         <v>742</v>
       </c>
@@ -13167,7 +13269,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
         <v>744</v>
       </c>
@@ -13192,7 +13294,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
         <v>748</v>
       </c>
@@ -13221,7 +13323,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
         <v>750</v>
       </c>
@@ -13246,7 +13348,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
         <v>753</v>
       </c>
@@ -13271,7 +13373,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
         <v>757</v>
       </c>
@@ -13296,7 +13398,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
         <v>759</v>
       </c>
@@ -13321,7 +13423,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
         <v>763</v>
       </c>
@@ -13350,7 +13452,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
         <v>765</v>
       </c>
@@ -13375,7 +13477,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
         <v>769</v>
       </c>
@@ -13400,7 +13502,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
         <v>773</v>
       </c>
@@ -13425,7 +13527,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
         <v>777</v>
       </c>
@@ -13450,7 +13552,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
         <v>779</v>
       </c>
@@ -13475,7 +13577,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
         <v>783</v>
       </c>
@@ -13500,7 +13602,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
         <v>785</v>
       </c>
@@ -13525,7 +13627,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
         <v>787</v>
       </c>
@@ -13550,7 +13652,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
         <v>789</v>
       </c>
@@ -13575,7 +13677,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
         <v>791</v>
       </c>
@@ -13600,7 +13702,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
         <v>793</v>
       </c>
@@ -13625,7 +13727,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
         <v>797</v>
       </c>
@@ -13650,7 +13752,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
         <v>799</v>
       </c>
@@ -13675,7 +13777,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
         <v>801</v>
       </c>
@@ -13700,7 +13802,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
         <v>803</v>
       </c>
@@ -13725,7 +13827,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
         <v>805</v>
       </c>
@@ -13750,7 +13852,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
         <v>807</v>
       </c>
@@ -13775,7 +13877,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
         <v>809</v>
       </c>
@@ -13800,7 +13902,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
         <v>811</v>
       </c>
@@ -13825,7 +13927,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
         <v>813</v>
       </c>
@@ -13850,7 +13952,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
         <v>819</v>
       </c>
@@ -13875,7 +13977,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
         <v>820</v>
       </c>
@@ -13900,7 +14002,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
         <v>821</v>
       </c>
@@ -13925,7 +14027,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
         <v>859</v>
       </c>
@@ -13950,7 +14052,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
         <v>861</v>
       </c>
@@ -13975,7 +14077,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
         <v>865</v>
       </c>
@@ -14000,7 +14102,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
         <v>873</v>
       </c>
@@ -14025,7 +14127,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
         <v>878</v>
       </c>
@@ -14050,7 +14152,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
         <v>879</v>
       </c>
@@ -14075,7 +14177,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
         <v>880</v>
       </c>
@@ -14100,7 +14202,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
         <v>881</v>
       </c>
@@ -14125,7 +14227,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
         <v>882</v>
       </c>
@@ -14150,7 +14252,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
         <v>896</v>
       </c>
@@ -14175,7 +14277,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
         <v>904</v>
       </c>
@@ -14200,7 +14302,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
         <v>906</v>
       </c>
@@ -14225,7 +14327,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
         <v>908</v>
       </c>
@@ -14254,7 +14356,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
         <v>910</v>
       </c>
@@ -14283,7 +14385,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
         <v>912</v>
       </c>
@@ -14312,7 +14414,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
         <v>915</v>
       </c>
@@ -14341,7 +14443,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
         <v>932</v>
       </c>
@@ -14366,7 +14468,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
         <v>933</v>
       </c>
@@ -14391,7 +14493,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
         <v>943</v>
       </c>
@@ -14416,7 +14518,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
         <v>944</v>
       </c>
@@ -14441,7 +14543,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
         <v>952</v>
       </c>
@@ -14466,7 +14568,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
         <v>953</v>
       </c>
@@ -14491,7 +14593,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
         <v>195</v>
       </c>
@@ -14520,7 +14622,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
         <v>959</v>
       </c>
@@ -14545,7 +14647,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
         <v>962</v>
       </c>
@@ -14570,7 +14672,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
         <v>974</v>
       </c>
@@ -14595,7 +14697,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
         <v>980</v>
       </c>
@@ -14620,7 +14722,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
         <v>987</v>
       </c>
@@ -14645,7 +14747,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
         <v>989</v>
       </c>
@@ -14674,7 +14776,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
         <v>999</v>
       </c>
@@ -14699,7 +14801,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
         <v>1003</v>
       </c>
@@ -14724,7 +14826,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
         <v>1012</v>
       </c>
@@ -14749,7 +14851,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
         <v>1247</v>
       </c>
@@ -14774,7 +14876,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
         <v>1250</v>
       </c>
@@ -14799,7 +14901,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
         <v>1253</v>
       </c>
@@ -14824,7 +14926,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
         <v>1256</v>
       </c>
@@ -14849,7 +14951,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
         <v>1259</v>
       </c>
@@ -14874,7 +14976,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
         <v>1262</v>
       </c>
@@ -14899,7 +15001,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
         <v>1267</v>
       </c>
@@ -14924,7 +15026,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
         <v>1278</v>
       </c>
@@ -14949,7 +15051,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
         <v>1283</v>
       </c>
@@ -14974,7 +15076,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
         <v>1003</v>
       </c>
@@ -14999,7 +15101,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
         <v>732</v>
       </c>
@@ -15024,7 +15126,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
         <v>631</v>
       </c>
@@ -15049,7 +15151,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
         <v>1289</v>
       </c>
@@ -15078,7 +15180,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
         <v>531</v>
       </c>
@@ -15103,7 +15205,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
         <v>1305</v>
       </c>
@@ -15128,7 +15230,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
         <v>1307</v>
       </c>
@@ -15153,7 +15255,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
         <v>1309</v>
       </c>
@@ -15178,7 +15280,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
         <v>1311</v>
       </c>
@@ -15203,7 +15305,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
         <v>1312</v>
       </c>
@@ -15228,7 +15330,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" s="2" t="s">
         <v>1314</v>
       </c>
@@ -15253,7 +15355,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" s="2" t="s">
         <v>1316</v>
       </c>
@@ -15278,7 +15380,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" s="2" t="s">
         <v>1318</v>
       </c>
@@ -15303,7 +15405,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" s="2" t="s">
         <v>1337</v>
       </c>
@@ -15332,7 +15434,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" s="2" t="s">
         <v>1346</v>
       </c>
@@ -15357,7 +15459,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
         <v>1347</v>
       </c>
@@ -15386,7 +15488,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
         <v>1362</v>
       </c>
@@ -15415,7 +15517,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
         <v>1366</v>
       </c>
@@ -15440,7 +15542,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" s="2" t="s">
         <v>1367</v>
       </c>
@@ -15465,7 +15567,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" s="2" t="s">
         <v>1368</v>
       </c>
@@ -15490,7 +15592,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" s="2" t="s">
         <v>1369</v>
       </c>
@@ -15515,7 +15617,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" s="2" t="s">
         <v>1370</v>
       </c>
@@ -15540,7 +15642,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
         <v>1371</v>
       </c>
@@ -15565,7 +15667,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
         <v>1372</v>
       </c>
@@ -15590,7 +15692,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
         <v>1374</v>
       </c>
@@ -15615,7 +15717,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" s="2" t="s">
         <v>1373</v>
       </c>
@@ -15640,7 +15742,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" s="2" t="s">
         <v>1414</v>
       </c>
@@ -15665,7 +15767,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
         <v>1421</v>
       </c>
@@ -15690,7 +15792,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
         <v>1442</v>
       </c>
@@ -15715,7 +15817,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
         <v>1448</v>
       </c>
@@ -15740,7 +15842,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
         <v>1465</v>
       </c>
@@ -15765,7 +15867,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
         <v>1468</v>
       </c>
@@ -15790,7 +15892,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" s="2" t="s">
         <v>1474</v>
       </c>
@@ -15815,7 +15917,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" s="2" t="s">
         <v>1479</v>
       </c>
@@ -15840,7 +15942,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A273" s="2" t="s">
         <v>1482</v>
       </c>
@@ -15869,7 +15971,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
         <v>1499</v>
       </c>
@@ -15894,7 +15996,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
         <v>1510</v>
       </c>
@@ -15923,7 +16025,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
         <v>1516</v>
       </c>
@@ -15952,7 +16054,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
         <v>1525</v>
       </c>
@@ -15977,7 +16079,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
         <v>1534</v>
       </c>
@@ -16006,7 +16108,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" s="2" t="s">
         <v>1539</v>
       </c>
@@ -16031,7 +16133,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" s="2" t="s">
         <v>1542</v>
       </c>
@@ -16056,7 +16158,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" s="2" t="s">
         <v>1551</v>
       </c>
@@ -16081,7 +16183,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" s="2" t="s">
         <v>1565</v>
       </c>
@@ -16106,7 +16208,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" s="2" t="s">
         <v>137</v>
       </c>
@@ -16131,7 +16233,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" s="2" t="s">
         <v>1581</v>
       </c>
@@ -16156,7 +16258,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" s="2" t="s">
         <v>1591</v>
       </c>
@@ -16181,8 +16283,116 @@
         <v>1593</v>
       </c>
     </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A286" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E286" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F286" s="2"/>
+      <c r="G286" s="2"/>
+      <c r="H286" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="I286" s="2" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A287" s="2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F287" s="2"/>
+      <c r="G287" s="2"/>
+      <c r="H287" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="I287" s="2" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A288" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="F288" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="G288" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="H288" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I288" s="2" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A289" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="F289" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G289" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="H289" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I289" s="2" t="s">
+        <v>1612</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I285"/>
+  <autoFilter ref="A1:I286"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
